--- a/src/attributions/attributions_ig_traj_480.xlsx
+++ b/src/attributions/attributions_ig_traj_480.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.02564990855633708</v>
+        <v>0.0257752081743409</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1026864474560563</v>
+        <v>0.0319767947619559</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05178107914796409</v>
+        <v>-0.02875478051642868</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07457535134340992</v>
+        <v>0.09926387462213426</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0101664151436978</v>
+        <v>0.002167322340954146</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00121152349820406</v>
+        <v>0.0005534795714547157</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,25 +1619,25 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1037971497368005</v>
+        <v>-0.02094518912720961</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05490289314248917</v>
+        <v>0.02330941961797073</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01887790020962058</v>
+        <v>-0.05056313127254117</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -1646,103 +1646,103 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0104239593636772</v>
+        <v>0.01045422227275444</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.006468212741984963</v>
+        <v>-0.01986705422411385</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07125182332171255</v>
+        <v>-0.01069644687266916</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.003356878942965723</v>
+        <v>0.005430042670353501</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.03809017470049671</v>
+        <v>-0.03685363375631654</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1003264915203136</v>
+        <v>-0.09388069186060483</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.04104423677005939</v>
+        <v>-0.1168394653519999</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3574507714600186</v>
+        <v>0.02246610590973051</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3122492023307003</v>
+        <v>-0.1766989847534006</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.02243038579700792</v>
+        <v>0.01030671979827504</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.006723227318897829</v>
+        <v>0.001377781879899703</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-2.110984874671346e-11</v>
+        <v>3.387875991119362e-11</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,28 +1754,28 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.03405405130283661</v>
+        <v>0.04230669538653412</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.02404008244944152</v>
+        <v>-0.01045080490043143</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2769798857393019</v>
+        <v>0.06036104850339091</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,73 +1784,73 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.03410463096003311</v>
+        <v>-0.1098038450106463</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2174150419767079</v>
+        <v>0.08711139896930065</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.03729336312796019</v>
+        <v>-0.08313527407905293</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.06581263146970631</v>
+        <v>0.06023945207844223</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.05399096979564769</v>
+        <v>-0.01960979100132516</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.09969791269228251</v>
+        <v>0.0615785878839224</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0006431495597019471</v>
+        <v>0.003946011021709895</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1056840541630064</v>
+        <v>-0.006159113120944582</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2479066825945224</v>
+        <v>-0.0560096157010111</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1859,31 +1859,31 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.0885778276627063</v>
+        <v>0.05104203294241784</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.03653084089433931</v>
+        <v>-0.03160620356095181</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.06129695581364261</v>
+        <v>0.02593346739741614</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,49 +1892,49 @@
         <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0008493822179330464</v>
+        <v>0.03681761694264957</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.001389971797153228</v>
+        <v>0.000372360193070998</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.124152897336232</v>
+        <v>0.1381942481019573</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.05630310226151081</v>
+        <v>0.05826839040765742</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.05163304115603058</v>
+        <v>0.01650176140474494</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.3363956135637374</v>
+        <v>-0.0532888475210704</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1943,106 +1943,106 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.04723067624648382</v>
+        <v>0.03784811046822189</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.02213491229899991</v>
+        <v>0.08867629330677432</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.04115224397155032</v>
+        <v>-0.04015554407781668</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.04855793544266188</v>
+        <v>0.03149057630456759</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.09097275424774388</v>
+        <v>0.001617355800702036</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0437153833291714</v>
+        <v>0.04866300004684944</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.03355535428023812</v>
+        <v>0.00494987107020389</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.07023172237214587</v>
+        <v>-0.0005707108102659166</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.03875348771430522</v>
+        <v>0.08109022009295516</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.06416941277510316</v>
+        <v>0.05734592781701502</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.04148314914040786</v>
+        <v>-0.03830269024970025</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02994457345216698</v>
+        <v>0.0358261942471468</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,25 +2051,25 @@
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.05106040363468346</v>
+        <v>0.1456817330460032</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0.005524844982535849</v>
+        <v>-0.006337719361497728</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.02954198982548959</v>
+        <v>0.01922793771129342</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.005476348722483906</v>
+        <v>0.1296662947998624</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.002143640567012754</v>
+        <v>0.0009936761576493278</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.008088945139443028</v>
+        <v>0.005287609339737241</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2108,48 +2108,48 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.0069538456345994</v>
+        <v>0.09655384384959144</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0160434845584447</v>
+        <v>0.001706663080566516</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1107177329193055</v>
+        <v>0.06433781167659949</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.681979172875198e-11</v>
+        <v>-3.311313743453e-11</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02930594100542004</v>
+        <v>-0.007318098047982284</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03586036804727369</v>
+        <v>0.03004551444609546</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05724129029898122</v>
+        <v>0.05146084515936118</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.004068412585987469</v>
+        <v>-0.001176981165569328</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2188,85 +2188,85 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1124861303635516</v>
+        <v>0.03226212202529545</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01975976762570621</v>
+        <v>-0.02566363038507286</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06628858367831653</v>
+        <v>-0.01361748683343478</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.00682045386146013</v>
+        <v>-0.006429801537138761</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.002940451493324927</v>
+        <v>-0.007916789260452676</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.001478632429067644</v>
+        <v>-0.01389358555193945</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03855885616097961</v>
+        <v>0.05749294306096548</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03672091176704607</v>
+        <v>-0.01693410118127828</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0084976865541549</v>
+        <v>0.02709320661729336</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3062877703100483</v>
+        <v>0.1678589571885542</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01323942496419567</v>
+        <v>-0.03649237764068858</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1355062998660338</v>
+        <v>-0.05532579420269389</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.0008039299806131785</v>
+        <v>-0.004490226773719603</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01317477827151414</v>
+        <v>-0.003379230636572816</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01009731300736082</v>
+        <v>-0.002479616534095442</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.01653120586324076</v>
+        <v>-0.004780000339546857</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0770645157417381</v>
+        <v>0.01220744002741232</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0164751078651627</v>
+        <v>0.0358041512163072</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,73 +2356,73 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1855462248174809</v>
+        <v>0.1190378615522727</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01441502301379133</v>
+        <v>-0.03379931183031276</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02071013834044515</v>
+        <v>0.002986617964479951</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.06269036177913695</v>
+        <v>-0.05776109554403003</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001882421259204991</v>
+        <v>0.04093481488785746</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.005280566650399286</v>
+        <v>0.002971073816761939</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02228584654188593</v>
+        <v>-0.03560957120389274</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.05781072429352292</v>
+        <v>0.04952331371150079</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1240472654739096</v>
+        <v>0.03383898344230889</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2434,52 +2434,52 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.0535667396603614</v>
+        <v>-0.06146019267933156</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0248700858610328</v>
+        <v>0.04631348745936789</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.001562938553484479</v>
+        <v>0.005136416124996417</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05004365343657451</v>
+        <v>-0.02723147261925325</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-9.568124671137028e-05</v>
+        <v>-0.003177828167897026</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0003181895044996771</v>
+        <v>0.0006837956856124317</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07256711973585216</v>
+        <v>-0.03202909974669517</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0500742514357739</v>
+        <v>0.01211158668853093</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.0312915567912712</v>
+        <v>-0.02984125836509779</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,16 +2518,16 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.04633183963782372</v>
+        <v>0.02584801386112187</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.03763326547794899</v>
+        <v>0.03708397546389444</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.006896743937185488</v>
+        <v>-0.01045791579135524</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
@@ -2539,22 +2539,22 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.03153470577043938</v>
+        <v>-0.04310549779621205</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.02377078630953142</v>
+        <v>0.03264268755262943</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01860215495681505</v>
+        <v>0.00977506177220879</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
@@ -2563,7 +2563,7 @@
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.0346454965572246</v>
+        <v>-0.034231602279566</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.00765457653150945</v>
+        <v>-0.03360676381655307</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.00595585622877305</v>
+        <v>0.004803269650745116</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,73 +2599,73 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.05680842205648695</v>
+        <v>-0.06655887813562443</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01021432691438925</v>
+        <v>0.0444467583562646</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.01464284430874264</v>
+        <v>-9.269213237733567e-05</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.008227679662497711</v>
+        <v>-0.02540293606733981</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03741870451186554</v>
+        <v>0.005885043876528573</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.00971214452247627</v>
+        <v>-0.001365578255302887</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001397145162371557</v>
+        <v>0.001218168585772702</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.01134866760871492</v>
+        <v>0.06441437564704586</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0002840895698628297</v>
+        <v>-0.0004737643991901435</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.0194802217615647</v>
+        <v>-0.0511299741145667</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02088836461491402</v>
+        <v>0.02548820901029863</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02283070417105195</v>
+        <v>0.1501418106573051</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02644257426156821</v>
+        <v>0.04397702007108261</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01149087017342303</v>
+        <v>-0.03627511219035121</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,52 +2736,52 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003928337452306454</v>
+        <v>0.09261287726662355</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0103610501169361</v>
+        <v>0.001197442616154287</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004558972662536946</v>
+        <v>0.0149022113853431</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.003316353241896798</v>
+        <v>0.1069096453696842</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.023787452808908</v>
+        <v>-0.08888444230494205</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01851361251844975</v>
+        <v>0.02609618636549729</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,34 +2790,34 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004784695526451315</v>
+        <v>-0.007069764566705031</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003209643386284302</v>
+        <v>-0.03604651649708261</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002509341176838409</v>
+        <v>-0.005019957734371952</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01113842547258861</v>
+        <v>0.08874076486453079</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,67 +2826,67 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01763812563569036</v>
+        <v>0.04907145147731181</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.004618250494758511</v>
+        <v>-0.06002795212375829</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04794670598605777</v>
+        <v>0.323779746147629</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0568534978375571</v>
+        <v>-0.1109096931648211</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01736336364263665</v>
+        <v>-0.1092736029961216</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.004678509164367342</v>
+        <v>0.0004396186565611324</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.004211391692067219</v>
+        <v>0.001485857278586883</v>
       </c>
       <c r="BH5" t="n">
-        <v>-5.747112392096058e-12</v>
+        <v>-2.152563801315944e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03461683035067201</v>
+        <v>-0.006481269560910788</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01492450401019315</v>
+        <v>0.0728507890651621</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01023073639803935</v>
+        <v>0.07064401224587326</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02196831225706507</v>
+        <v>0.2844688661632984</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02208866572857491</v>
+        <v>-0.006268037647498088</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.00674710085654607</v>
+        <v>-0.05449632791425059</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003333270710565289</v>
+        <v>-0.1006143587301098</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
@@ -2961,25 +2961,25 @@
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01397458694496194</v>
+        <v>-0.04632778471644312</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01433515909511486</v>
+        <v>0.05238502433666685</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004083068912409761</v>
+        <v>-0.07655806563629289</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
@@ -2988,43 +2988,43 @@
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002242100947894175</v>
+        <v>0.03020043394763653</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.004938151883474152</v>
+        <v>0.02940650955983799</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.003140986538204125</v>
+        <v>-0.08653277510156251</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01370895667569421</v>
+        <v>-0.05496286888862739</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02119106438186492</v>
+        <v>0.05343125914290027</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01419425528854681</v>
+        <v>-0.01866804161331062</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01970582164499048</v>
+        <v>-0.05463826624046138</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.0030305017372534</v>
+        <v>0.008446469502756002</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.007598774766138293</v>
+        <v>-0.06942673854150194</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01803458856898171</v>
+        <v>-0.007755162739569789</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01226034957526392</v>
+        <v>0.006106477767027982</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,19 +3087,19 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01940294934061972</v>
+        <v>0.08772621348233206</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02213035121734672</v>
+        <v>-0.05724722283970397</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.0008225235812763002</v>
+        <v>0.07438547995367434</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001113956594069263</v>
+        <v>-0.001137771095441969</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001616649296827816</v>
+        <v>-0.08991147259575009</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0163823475985723</v>
+        <v>-0.02059484334535802</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01189883688838667</v>
+        <v>-0.04579989396718079</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02533177249061063</v>
+        <v>-0.1299913086273069</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01131635613135916</v>
+        <v>0.08655002312489483</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.006662017127938505</v>
+        <v>-0.1004086690979587</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,79 +3177,79 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0129873692179908</v>
+        <v>-0.06489425266602213</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01739898688136565</v>
+        <v>0.03768481979013982</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0211576674925422</v>
+        <v>-0.03713692374614742</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0311623451078888</v>
+        <v>-0.01319178516244617</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01400388364899286</v>
+        <v>0.03403546937822574</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.002041229422259724</v>
+        <v>0.02224566678543726</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0002583003445861744</v>
+        <v>0.003066863230643617</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01815658572768531</v>
+        <v>-0.07233732831479389</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01337246841853525</v>
+        <v>-0.04920645072006612</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.0003347521322964405</v>
+        <v>0.02021472564676042</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8267166692618977</v>
+        <v>0.1056104753368705</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1858383659967455</v>
+        <v>-0.03540228606054042</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01882878377789432</v>
+        <v>-0.01756267471536577</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4204548517893946</v>
+        <v>0.09192598223227237</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02711629709904473</v>
+        <v>0.007536662212300273</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08298395290753893</v>
+        <v>-0.01955576770535564</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3898,52 +3898,52 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.247027770540046</v>
+        <v>0.033220325528524</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2177253628700377</v>
+        <v>-0.02870515387542195</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1056078654360426</v>
+        <v>-0.02873448585856219</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0668834066517628</v>
+        <v>-0.005118028799854886</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.03582072441112787</v>
+        <v>-0.009698497080345659</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.005257789935443159</v>
+        <v>-0.01791462755603661</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3952,25 +3952,25 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1881479138609334</v>
+        <v>0.07018890600599077</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1371206214276454</v>
+        <v>-0.02241072303985966</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1068795508710572</v>
+        <v>0.02396450802721913</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.417191647218845</v>
+        <v>0.1945101784961971</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1315853580259561</v>
+        <v>-0.06702266799721061</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3887696451997214</v>
+        <v>-0.07836781845348791</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.07596082206495709</v>
+        <v>-0.01201059852091808</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.04181198414561192</v>
+        <v>-0.008604972672816879</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1266425949409781</v>
+        <v>-0.008871380057067049</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,31 +4027,31 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1760570126300071</v>
+        <v>0.001929660509824821</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.3148184705817483</v>
+        <v>0.01903124422211624</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1247102651359897</v>
+        <v>0.05020567230920202</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.706066917254768</v>
+        <v>0.1354975651849569</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.05162849228262997</v>
+        <v>-0.02992573749224827</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.002435113002976967</v>
+        <v>-0.02083509303588361</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.3050420891988065</v>
+        <v>-0.06045180576246673</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.07154537520762064</v>
+        <v>0.04826555140083413</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.1044159059268344</v>
+        <v>0.008246710567879845</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.005407429821955471</v>
+        <v>-0.03081721863186263</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2854390447730079</v>
+        <v>0.05715401431019645</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.2440290683718539</v>
+        <v>0.03661687775333287</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,52 +4138,52 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.2381563784269803</v>
+        <v>-0.06362695623993066</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1720882100645461</v>
+        <v>0.05491586502079471</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.1058179038054158</v>
+        <v>0.0142716385548139</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1195925015237232</v>
+        <v>-0.02158892626837819</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.03274886929072002</v>
+        <v>-0.004898638748974882</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01361024422477402</v>
+        <v>-0.00671710862714803</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1503328660543503</v>
+        <v>-0.03998767039195996</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1072525170841541</v>
+        <v>0.01450501011621122</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.08412114572995145</v>
+        <v>-0.03095819052373996</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.01928912035584491</v>
+        <v>0.009967383727095363</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.08853512987536069</v>
+        <v>0.02865498054219124</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.2382288180180868</v>
+        <v>-0.01162515061548284</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4249,52 +4249,52 @@
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1420861840336718</v>
+        <v>-0.03761659515291038</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07189636249003994</v>
+        <v>0.04339811376716893</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.02007987575028096</v>
+        <v>0.006468611106681173</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.2315724380864625</v>
+        <v>-0.03588584283316295</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.1872329214043918</v>
+        <v>-0.03310477618458323</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1958266414892591</v>
+        <v>-0.001393538893130221</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2549055092326479</v>
+        <v>-0.0694957746697948</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.1184103185806247</v>
+        <v>0.05073527042338151</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.1172019248550936</v>
+        <v>0.005916199086805438</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.06716915434265404</v>
+        <v>-0.04045957338194298</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1466223644446846</v>
+        <v>0.01607733874724863</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.1113019362247518</v>
+        <v>0.0209019057329909</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,28 +4354,28 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05126894984647484</v>
+        <v>0.001668361971262674</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.2025443076586377</v>
+        <v>0.09355087712573626</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1691454427315452</v>
+        <v>-0.01748853412032536</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1324750414424558</v>
+        <v>-0.0460831373546481</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.08766313477453287</v>
+        <v>0.008560959198789483</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,25 +4985,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07271438566524605</v>
+        <v>0.1255031198717333</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01001903904513703</v>
+        <v>0.01086337885407027</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01970662048424632</v>
+        <v>-0.0393494316614344</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02320567331011206</v>
+        <v>0.1589576490549975</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02223296472741166</v>
+        <v>-0.01056230718053335</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009153131829486056</v>
+        <v>0.0105814626231593</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
@@ -5036,49 +5036,49 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.005089983445757113</v>
+        <v>0.03878974621632993</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01919720254128989</v>
+        <v>-0.04995640466613958</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0175815665099796</v>
+        <v>0.03241444352203874</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.004677791815491733</v>
+        <v>-0.00532526892942935</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.008010172466597971</v>
+        <v>-0.02234162484538984</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0008771381649836944</v>
+        <v>-0.000291292163172019</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5087,13 +5087,13 @@
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01396840664085086</v>
+        <v>0.06877807287858362</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,25 +5102,25 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01310370168347367</v>
+        <v>0.001234898355008778</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01660863745641741</v>
+        <v>-0.06096667419792638</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1060055617798081</v>
+        <v>0.2902409478970606</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,10 +5129,10 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.094592385439866e-05</v>
+        <v>-0.07009011175223684</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.0185734663812924</v>
+        <v>-0.09094334006799731</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,40 +5141,40 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01458954772394468</v>
+        <v>-0.02255267178818702</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01255868709376587</v>
+        <v>-0.03005093827032774</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.00385140418919364</v>
+        <v>-0.007514223742403557</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04156272843272179</v>
+        <v>0.01195651880164337</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,16 +5183,16 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02815366938379407</v>
+        <v>0.08408494457360954</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01442015374317063</v>
+        <v>0.06068666793920038</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.03989398262038085</v>
+        <v>0.1710817679666267</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.03016721426211118</v>
+        <v>-0.006288568611690289</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02586286458016209</v>
+        <v>-0.02865015545529871</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.009849564437785584</v>
+        <v>-0.05870732330174285</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.002190312879195378</v>
+        <v>0.003600015843984367</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01723270987225491</v>
+        <v>0.03701515834677079</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,55 +5252,55 @@
         <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01564881945047198</v>
+        <v>-0.03930735934949633</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.009832099366567676</v>
+        <v>0.1029851049784736</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03017767584038514</v>
+        <v>0.002282023034144928</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.003435443677792604</v>
+        <v>-0.0530728921594341</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0007922005302711486</v>
+        <v>0.004639350515433838</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02225819773657076</v>
+        <v>0.04312703348727494</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,25 +5309,25 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01569052706398947</v>
+        <v>-0.004326039429948455</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02202764610680785</v>
+        <v>-0.03771826903996975</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01596385185880919</v>
+        <v>0.07728967548543801</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.003061651699064285</v>
+        <v>-0.04618085676797532</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02053396948489229</v>
+        <v>-0.01922913259517004</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.005363442303036215</v>
+        <v>0.02206682717631561</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03034138578463879</v>
+        <v>0.01222066120474121</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04606333958009004</v>
+        <v>-0.09416510228682967</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01316308739049188</v>
+        <v>0.01051637701876476</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.002110256039133473</v>
+        <v>0.006986714363521515</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.009015903686943079</v>
+        <v>-0.02536633449701922</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002219295279438191</v>
+        <v>-0.01407901456440662</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.006336789678923107</v>
+        <v>-0.008505774195916105</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01080583833120833</v>
+        <v>-0.1048416113203366</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.05575866786337145</v>
+        <v>-0.1276584783161257</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002431056234970435</v>
+        <v>-0.06069488306225757</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0009703860014717932</v>
+        <v>-0.008482453785518887</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0222632993904779</v>
+        <v>0.02757046994077877</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,19 +5471,19 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02372737263249598</v>
+        <v>-0.0639200134163614</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.05102383061660412</v>
+        <v>0.04119873627752155</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.008984822058765494</v>
+        <v>0.009555784393787379</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
@@ -5495,40 +5495,40 @@
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.002789923882549848</v>
+        <v>0.01288396921744869</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01317368738783292</v>
+        <v>0.002727033147225625</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04545820137093</v>
+        <v>-0.08993152221805818</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02394657649452682</v>
+        <v>-0.01479173828196982</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.005195511395563743</v>
+        <v>-0.02474059318128829</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1945945989842819</v>
+        <v>0.1707558294068401</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.04669317057528266</v>
+        <v>-0.05239125017684236</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04992812409058424</v>
+        <v>-0.04167644850595421</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,22 +5575,22 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1263583660604587</v>
+        <v>0.1574589035449234</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01580227072829481</v>
+        <v>-0.02485001682493779</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06175485414304914</v>
+        <v>-0.05539319130843726</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5602,85 +5602,85 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06104064209349854</v>
+        <v>0.05577570453480729</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01319646710917136</v>
+        <v>-0.03013269200989857</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03205492462254451</v>
+        <v>-0.03535877507238754</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01842125219319892</v>
+        <v>-0.009349056790606993</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01261485963816232</v>
+        <v>-0.01347848096117531</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0009496414074324008</v>
+        <v>-0.02723611106561065</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.023001977710809</v>
+        <v>0.08542229176882596</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.04490306489349971</v>
+        <v>-0.02287166263199649</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05304550033678351</v>
+        <v>0.03007622247085891</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3347785821722867</v>
+        <v>0.2392385232123631</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.02923103304566301</v>
+        <v>-0.0793835399418769</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1595418300799357</v>
+        <v>-0.1093305053703366</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01151565566659895</v>
+        <v>-0.02199557426285019</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.01545413702165327</v>
+        <v>-0.008429880719668704</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06597212640442464</v>
+        <v>-0.01957374566197448</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07605431519986099</v>
+        <v>0.005429115218886581</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06187503459631215</v>
+        <v>0.02690045453132627</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1017724074163456</v>
+        <v>0.04859551825894519</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,130 +5770,130 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1721766301529281</v>
+        <v>0.1898351407031648</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.003263228641258105</v>
+        <v>-0.06519149895182565</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01729911275267216</v>
+        <v>-0.03647624030061231</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05591284645106485</v>
+        <v>-0.07479841313824802</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.004703755305595964</v>
+        <v>0.06342409416830073</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006022321430624198</v>
+        <v>0.009735075836985924</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.04008695070717644</v>
+        <v>-0.04633078261519951</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.04815796312381088</v>
+        <v>0.06606935534909221</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09622293532641159</v>
+        <v>0.03623761229472699</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0295037222120496</v>
+        <v>-0.07665658007668485</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02938521846981641</v>
+        <v>0.07184399972465179</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01361321927185633</v>
+        <v>0.01880668631550371</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.04653060684835367</v>
+        <v>-0.06899129573579971</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01336007291177631</v>
+        <v>0.05462956222871334</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.0150270411398336</v>
+        <v>-0.02845218475504129</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,76 +5905,76 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.04094232820786543</v>
+        <v>-0.04030589506030505</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.06202111267336752</v>
+        <v>0.02190645014322612</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.002806458834372753</v>
+        <v>-0.02991141585294779</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04750821817449326</v>
+        <v>0.02958129420064035</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.04681322939119825</v>
+        <v>0.03631371844437086</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03185090029374527</v>
+        <v>-0.0267591778917684</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02683950545464508</v>
+        <v>-0.03296470260460332</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.08144751429269721</v>
+        <v>0.05736819778663849</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05339732193474144</v>
+        <v>0.006555450103652798</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,139 +5983,139 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05703102843969719</v>
+        <v>-0.05089631545077555</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.06862634542776522</v>
+        <v>-0.04805143550572458</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02165972469861102</v>
+        <v>-0.01429215756666946</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04756871241504559</v>
+        <v>-0.0857864054457282</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01948912976489972</v>
+        <v>0.06962646516114851</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01202247585981431</v>
+        <v>0.007463868913124407</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05295705160814142</v>
+        <v>-0.0425884405796323</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.05282865948021772</v>
+        <v>0.02946555346664543</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02641351711978296</v>
+        <v>0.01386220840175647</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01770561774300478</v>
+        <v>0.002725146259163106</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.01812201718233876</v>
+        <v>0.07654872251431263</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0232107074501411</v>
+        <v>-0.02423450650461056</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01026867341472875</v>
+        <v>-0.04929897531946388</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03051470815865971</v>
+        <v>0.01171394453040705</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2135166761811174</v>
+        <v>0.05563840953155023</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.009227368469172693</v>
+        <v>-0.006573598726343602</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03147956898919432</v>
+        <v>-0.02499717086953425</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1185143264057585</v>
+        <v>0.06770181175252182</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.004625114879605786</v>
+        <v>0.003556819541294737</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03211632118395092</v>
+        <v>-0.03153137153842281</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,19 +6746,19 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05987676905695381</v>
+        <v>0.02126965713398519</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01860124229089936</v>
+        <v>-0.009761685097456342</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04676193506428838</v>
+        <v>-0.004582257975500539</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6773,43 +6773,43 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01592318707869908</v>
+        <v>-0.004695825596271359</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.002166635984681108</v>
+        <v>-0.007213328786462012</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001918171449303482</v>
+        <v>-0.01153008986549001</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0007868075901159387</v>
+        <v>0.03533557447255892</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01940599450381241</v>
+        <v>-0.002366912597424735</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03143854868790466</v>
+        <v>0.02504450438735388</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6824,46 +6824,46 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2881072818263514</v>
+        <v>0.09999779558947559</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02766379429611514</v>
+        <v>-0.00725025238437373</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08402186873695046</v>
+        <v>-0.04924280393629237</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02124134422304049</v>
+        <v>-0.02394023202433377</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02840324305154208</v>
+        <v>-0.0007420323976778159</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03449833784223652</v>
+        <v>-0.00938126435090467</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09848596185583899</v>
+        <v>0.02178318318280381</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01500760134649407</v>
+        <v>0.01826305167459095</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1099697790187503</v>
+        <v>0.03444156594696225</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,43 +6908,43 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1449917969791802</v>
+        <v>0.08319616588241859</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01624954957727637</v>
+        <v>-0.03166461100981697</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.03254319757507516</v>
+        <v>-0.011072730747383</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05602195398454066</v>
+        <v>-0.02182722617407771</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.004969890181694247</v>
+        <v>0.021186739012691</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004174710074630878</v>
+        <v>0.01726033063717946</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6962,22 +6962,22 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03928978767011475</v>
+        <v>-0.03117656006741035</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03394431693629183</v>
+        <v>0.01606266340876551</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06427478790170311</v>
+        <v>0.02693383059636991</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03874488978904579</v>
+        <v>-0.02295925620210082</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.00632225484876316</v>
+        <v>0.02644731199650325</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.003306626885524905</v>
+        <v>0.01478719235844771</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7013,100 +7013,100 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.01328918308028572</v>
+        <v>0.0008545385095938908</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03099542569994594</v>
+        <v>0.005393977885765805</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.007147539298953422</v>
+        <v>-0.001557625283698949</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06613063622134778</v>
+        <v>-0.021390847175871</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.01572109109812926</v>
+        <v>-0.01374973902183345</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.003005039691796762</v>
+        <v>-0.01174744539367854</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01131162848799969</v>
+        <v>0.03284647720848698</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02047689460926528</v>
+        <v>0.01319970396206194</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.0330667230204665</v>
+        <v>-0.04843180385050965</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03133300440849108</v>
+        <v>0.008462704460107251</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.006715592488939278</v>
+        <v>0.01580305869486195</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02436804764643175</v>
+        <v>0.02521273377113542</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,103 +7124,103 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03954302200613345</v>
+        <v>-0.01325597670037475</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.004007529329772861</v>
+        <v>0.02263700966927859</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02127764524265502</v>
+        <v>-0.002902195834026359</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.04138770074807067</v>
+        <v>-0.02494192409550022</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0005293468562711213</v>
+        <v>0.02787156693791316</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01706400233114441</v>
+        <v>0.01194464438400231</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.02516510508322213</v>
+        <v>0.004911811418567625</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01644761367888051</v>
+        <v>0.005228122939036108</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01501943028015303</v>
+        <v>-0.01811380487879726</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04908535748692393</v>
+        <v>0.01159484366682967</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.03816819040045814</v>
+        <v>0.02320795341404885</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.001133201984589859</v>
+        <v>-0.04054250197981926</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
@@ -7232,28 +7232,28 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002071354134359718</v>
+        <v>0.005371516776306497</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03603919848420074</v>
+        <v>-0.004478038383679321</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,25 +7261,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2361640604239683</v>
+        <v>0.1072537086044433</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.002710868441795245</v>
+        <v>-0.04458401335827164</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1313881360486083</v>
+        <v>-0.03370487831098801</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1698742611902771</v>
+        <v>0.1594680692473985</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01267482012449292</v>
+        <v>-0.07286636860185182</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.09826969229365946</v>
+        <v>-0.01975346606343861</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01530298873676398</v>
+        <v>0.03532641693351152</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,25 +7324,25 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0435695076964552</v>
+        <v>-0.01376977307624169</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01108430958646125</v>
+        <v>-0.009027323208121937</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01715232491851998</v>
+        <v>-0.001874655493509137</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.008740774603372971</v>
+        <v>-0.020374073272899</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.001649140063158029</v>
+        <v>-0.001510057291613239</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0265635159102205</v>
+        <v>0.03764244422530252</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.02973925266292981</v>
+        <v>0.0220607648097425</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.06016192540879717</v>
+        <v>-0.01919057657688096</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,37 +7393,37 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2301958228706372</v>
+        <v>0.1569301706771346</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01622622770612801</v>
+        <v>-0.06086411702393814</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1139380095257308</v>
+        <v>-0.04557947873455476</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06415936795105978</v>
+        <v>-0.01434705077038382</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03127162964557279</v>
+        <v>-0.03632734862127204</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.02903176244150292</v>
+        <v>-0.01294957924072573</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.09494675270199043</v>
+        <v>0.0233431798810464</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,37 +7459,37 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.04640886073128865</v>
+        <v>0.04929463679310281</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01416048371698171</v>
+        <v>-0.007016826005349258</v>
       </c>
       <c r="BR13" t="n">
         <v>-0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1057740903133626</v>
+        <v>0.1343211470892951</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02576631047581773</v>
+        <v>-0.01827356612551782</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.02351604512281605</v>
+        <v>-0.02182887251271138</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,52 +7504,52 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.05482204172204132</v>
+        <v>-0.05250081412558794</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01206159953935418</v>
+        <v>0.02245252633929585</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04110323918646785</v>
+        <v>0.03064675273759704</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.01671939099618268</v>
+        <v>-0.0919591617751245</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0177238813094704</v>
+        <v>0.05585270785443831</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.0496681954864814</v>
+        <v>0.04433260634767949</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>0</v>
@@ -7558,25 +7558,25 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.03802637717231831</v>
+        <v>-0.04544005153239538</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01220307354880744</v>
+        <v>0.02052209993315997</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.04058399603689824</v>
+        <v>0.03046756034136911</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,46 +7585,46 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.007122145836578518</v>
+        <v>0.001749097862002241</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.004500776408022378</v>
+        <v>-0.01415914248161071</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001068010265608575</v>
+        <v>0.01350988156790075</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.02503024174871113</v>
+        <v>-0.04327172820742603</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03333834106167789</v>
+        <v>0.01791054016820074</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.007172720405565677</v>
+        <v>-0.03734828663728443</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7639,7 +7639,7 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01301036178271753</v>
+        <v>0.03072141629796259</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,13 +7648,13 @@
         <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.03891598934242668</v>
+        <v>-0.01104875966400124</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01111794124122876</v>
+        <v>-0.0696348323851006</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02805575100553454</v>
+        <v>0.01122050465593264</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,37 +7675,37 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.006585893604328159</v>
+        <v>0.006251059221196423</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.031410836730465</v>
+        <v>0.02123369509008607</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.04155478683573987</v>
+        <v>-0.02375746138211863</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03330034609963484</v>
+        <v>-0.01259933841510162</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07519401941890877</v>
+        <v>0.0360434673428834</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,31 +7714,31 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.03820327101122797</v>
+        <v>-0.05591929387301192</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.009478051766550595</v>
+        <v>0.01484174449098134</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04450983786457009</v>
+        <v>0.02780452776021306</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01658450399271957</v>
+        <v>-0.03778032848533022</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,37 +7756,37 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.0452638919648829</v>
+        <v>0.01440210986441237</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02232765914980213</v>
+        <v>0.01465508132826856</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01615892653418536</v>
+        <v>0.02242147973345508</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.02500917237632016</v>
+        <v>-0.04284329137095282</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.002533964782741453</v>
+        <v>0.001569496681170652</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7798,10 +7798,10 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02883108166131645</v>
+        <v>-0.003735152985509731</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03453484872708745</v>
+        <v>-0.00677896480764065</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7833,13 +7833,13 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.07947536165619459</v>
+        <v>-0.03024795661660334</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2195216885017011</v>
+        <v>0.0214204552033669</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.07620613765508161</v>
+        <v>-0.05215972369757254</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
@@ -7848,52 +7848,52 @@
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.08820296401274216</v>
+        <v>-0.02868254245440989</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2397627939277903</v>
+        <v>0.01390129572885285</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03832695128157132</v>
+        <v>-0.05077188465419091</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.04419274549187429</v>
+        <v>-0.01276103325199779</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07011806946823175</v>
+        <v>0.03055444260863481</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02048665639194936</v>
+        <v>0.004839021784366058</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
@@ -7905,7 +7905,7 @@
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.00938059216616606</v>
+        <v>-0.009292203054511481</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01393668039118827</v>
+        <v>-0.01692051715553588</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01896905793053639</v>
+        <v>-0.01427035456262695</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7935,25 +7935,25 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.007085623150200973</v>
+        <v>-0.03385299083089888</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.029143707420086</v>
+        <v>0.02813373612776717</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.03877926203550842</v>
+        <v>-0.004196387170230501</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -7962,19 +7962,19 @@
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.09000148952590316</v>
+        <v>-0.04863149984305482</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1671717946139749</v>
+        <v>0.1121218850826475</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1763930626109211</v>
+        <v>-0.08488852713371538</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7995,13 +7995,13 @@
         <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.01828971299029426</v>
+        <v>-0.001715866170883544</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.03908173396706774</v>
+        <v>-0.08785780481750809</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.03341626527136463</v>
+        <v>-0.03704171540670953</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,25 +8010,25 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.05014124378416669</v>
+        <v>0.03132409608463471</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.003490369424559308</v>
+        <v>0.04384242838388764</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.1477271161646111</v>
+        <v>0.0738115986773617</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,82 +8037,82 @@
         <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.09294040489869114</v>
+        <v>-0.04465122997366935</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1050148863211197</v>
+        <v>0.1096742222822664</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.1118399981256079</v>
+        <v>-0.01568461062732485</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.05348166127411752</v>
+        <v>0.03347707852991752</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.05295699188413459</v>
+        <v>0.004954448042276492</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.008630882248258724</v>
+        <v>0.0111183305562737</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.009605963927654601</v>
+        <v>0.008299429002442234</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.02519918504568076</v>
+        <v>0.01890700366163971</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.08466334486983589</v>
+        <v>0.05052386966160977</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,31 +8121,31 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.03638001014170766</v>
+        <v>0.02515342349931769</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.04501481438082879</v>
+        <v>0.003721563794692678</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01444406899890263</v>
+        <v>0.02103406315627911</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>-0</v>
@@ -8154,19 +8154,19 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.004889625609735782</v>
+        <v>0.01619144800629067</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.05551676611217288</v>
+        <v>-0.02007124852070355</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.009080945194535251</v>
+        <v>-0.0003496996041221616</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,58 +8175,58 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.05365368563182655</v>
+        <v>0.001698779707990139</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.02736327462247699</v>
+        <v>-0.009477161273971158</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.06846875861873329</v>
+        <v>0.0466862127171518</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.02423040877516672</v>
+        <v>-0.03196615122543847</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.02540467485597527</v>
+        <v>-0.01815949793736208</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.03140337343808956</v>
+        <v>-0.03963397023850247</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
         <v>0</v>
@@ -8235,22 +8235,22 @@
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.06341883140698014</v>
+        <v>0.005451705533932896</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.06647761513635328</v>
+        <v>0.01791791778643612</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.0276834338561475</v>
+        <v>-0.004746549321015271</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,52 +8259,52 @@
         <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.03646709211001833</v>
+        <v>-0.004094929496630416</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.04403014975759904</v>
+        <v>-0.01185548489759958</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.005526456081577553</v>
+        <v>0.008855120063562942</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
         <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.04761467193655244</v>
+        <v>0.0260073105132262</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.05029265353874018</v>
+        <v>-0.00734836676889362</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.01448174607961733</v>
+        <v>0.01301051567725007</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
@@ -8316,25 +8316,25 @@
         <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.01896739375584535</v>
+        <v>0.03614503318052321</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.04567358658122016</v>
+        <v>-0.01266180620043119</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.05159732059200937</v>
+        <v>-0.0518949313020302</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,16 +8343,16 @@
         <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.006902175778820947</v>
+        <v>-0.001528016812906146</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.003608961790806579</v>
+        <v>0.004985208987114942</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.01296345096752041</v>
+        <v>0.04998407577301218</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,37 +8361,37 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.02465136886765408</v>
+        <v>0.02526735985095347</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.02943341324445911</v>
+        <v>-0.03089662467618545</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8965,22 +8965,22 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2314015914684155</v>
+        <v>0.1890421357218223</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2160726929515598</v>
+        <v>-0.04697313491785071</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06165566100280131</v>
+        <v>-0.06437217386965668</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8995,7 +8995,7 @@
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1634604177489661</v>
+        <v>0.2844970035316047</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
@@ -9004,13 +9004,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2085714579633544</v>
+        <v>-0.09202151692389433</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06784139566612128</v>
+        <v>-0.06126415224115193</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9019,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.05445293584038472</v>
+        <v>0.07092893081604613</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,25 +9031,25 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02356280591961959</v>
+        <v>-0.06126138468975172</v>
       </c>
       <c r="X16" t="n">
-        <v>0.05290990656313841</v>
+        <v>0.01213419390378965</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.03022167422121979</v>
+        <v>-0.02439446887789163</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
@@ -9058,10 +9058,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.0007578729994357498</v>
+        <v>-0.07005541233732294</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.009774911792270146</v>
+        <v>0.01453167657318201</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9073,136 +9073,136 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.06283657098031549</v>
+        <v>0.01412468355021714</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01926992395310439</v>
+        <v>-0.06900937100899249</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.02544534873716735</v>
+        <v>-0.02994991985974409</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2358411352982727</v>
+        <v>0.3324219654034946</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1166222217039558</v>
+        <v>-0.1665768636168774</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.05172647690616296</v>
+        <v>-0.09673143930999401</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05279915072791297</v>
+        <v>-0.04832106496362339</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.121715513291481</v>
+        <v>-0.03430979759660315</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.01961551264578803</v>
+        <v>0.008957406925022768</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.09854552412794979</v>
+        <v>0.09888522474579467</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02976666480261161</v>
+        <v>0.1005859450474334</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.05356562683222825</v>
+        <v>0.04949049554026011</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1439683025657552</v>
+        <v>0.201484429229851</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.05455392503247397</v>
+        <v>-0.05688418407159247</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.02794386572656225</v>
+        <v>-0.02178758523727925</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
@@ -9211,25 +9211,25 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03604966116736702</v>
+        <v>-0.06624011697848572</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.03928721216543642</v>
+        <v>0.04151803379382651</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02598147576526526</v>
+        <v>0.02938272526751707</v>
       </c>
       <c r="CJ16" t="n">
         <v>-0</v>
       </c>
       <c r="CK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL16" t="n">
         <v>-0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.02684752404740958</v>
+        <v>-0.135520919458558</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.001543179930594911</v>
+        <v>0.1172168402304239</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01601786989268745</v>
+        <v>-0.003061348844269588</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9265,19 +9265,19 @@
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01767025713173526</v>
+        <v>-0.05995736184638915</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.03719263977655044</v>
+        <v>0.01768749543936855</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03448935463383605</v>
+        <v>0.03459752009622281</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9289,49 +9289,49 @@
         <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04173650856022698</v>
+        <v>-0.05399085845838406</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02600775332442632</v>
+        <v>-0.01781530244065465</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.004443777981840651</v>
+        <v>-0.02610775262791406</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03135799457285534</v>
+        <v>-0.0248509762201479</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01954445159580168</v>
+        <v>-0.005584018587584623</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.07695144380279248</v>
+        <v>-0.03237927367702623</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9343,10 +9343,10 @@
         <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.007479216668150336</v>
+        <v>0.03946956497074863</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,37 +9355,37 @@
         <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06268434397862228</v>
+        <v>-0.03193690107963817</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.05352761695318281</v>
+        <v>-0.01076570802835916</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01709370376705555</v>
+        <v>-0.0101712112760245</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0369286582472762</v>
+        <v>-0.005979201304053653</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.007418024491213002</v>
+        <v>0.03985366167316955</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9394,58 +9394,58 @@
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.03395804504133794</v>
+        <v>0.002441216550530499</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.01324146363740701</v>
+        <v>-0.05847803949707008</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.05151556369466401</v>
+        <v>0.01392204929439874</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
         <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01306138067496084</v>
+        <v>-0.07491465302095933</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.03275343148799002</v>
+        <v>0.02537056861198348</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.03859949709384559</v>
+        <v>0.01980194670441154</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
         <v>-0</v>
@@ -9454,7 +9454,7 @@
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.04424539450667565</v>
+        <v>-0.05684442728563712</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.03836089470158582</v>
+        <v>0.09553260529703297</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02290937625518254</v>
+        <v>-0.00706289229624961</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.006726763276339746</v>
+        <v>0.006477705886910294</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,46 +9490,46 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.005534722254627096</v>
+        <v>-0.02048247011546966</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.001647918042723864</v>
+        <v>-0.02728746088427476</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.03312256500880027</v>
+        <v>-0.07643686401732593</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.04641492575661066</v>
+        <v>0.04430344804118112</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,16 +9537,16 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5550138069312383</v>
+        <v>0.3909277761816436</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2401849420405212</v>
+        <v>-0.2150063713593817</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1383491681489112</v>
+        <v>-0.02447466183293486</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.462213491185436</v>
+        <v>0.4254171895330871</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2500016339888427</v>
+        <v>-0.2609227352006054</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1877995025906109</v>
+        <v>-0.05390118789030009</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9588,55 +9588,55 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1495842836586147</v>
+        <v>0.1029238382635718</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001545900491536841</v>
+        <v>-0.05616751258556137</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0901368858592681</v>
+        <v>-0.08841429775170608</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1150890096828621</v>
+        <v>-0.05813554590846819</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.001237252366982664</v>
+        <v>-0.0725742172164429</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.002596233832805515</v>
+        <v>-0.07119195302360917</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -9645,22 +9645,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.07058231851774718</v>
+        <v>0.1259349458390268</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.03042678626650049</v>
+        <v>-0.08935373326835298</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.02699066190093766</v>
+        <v>0.04442758059884388</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,46 +9669,46 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4800699903238421</v>
+        <v>0.3665534241445461</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.007621599065822112</v>
+        <v>-0.1180395726938615</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1088008865265059</v>
+        <v>-0.1461639648547059</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05909281343064155</v>
+        <v>-0.009673402786988887</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.09839742907006416</v>
+        <v>-0.05548193425095834</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2378448880646889</v>
+        <v>-0.04284080701436973</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,22 +9726,22 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.06644667632955802</v>
+        <v>-0.02887286184106003</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.05225467265434003</v>
+        <v>0.006257611369202012</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.05037239295219405</v>
+        <v>0.07457480095796137</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9753,22 +9753,22 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2699143698200158</v>
+        <v>0.289278720674899</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.04276982915303876</v>
+        <v>-0.151547883335676</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.07768469768891621</v>
+        <v>-0.05063623474803779</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
@@ -9780,46 +9780,46 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.1178214169761398</v>
+        <v>-0.1264199604310566</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.031680140969163</v>
+        <v>0.1253166576075826</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.01441968022036105</v>
+        <v>0.008281812267413289</v>
       </c>
       <c r="CI17" t="n">
         <v>0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.04126602571261964</v>
+        <v>-0.1555055563124638</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.09169475560254579</v>
+        <v>0.2287165801771902</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1257119669488968</v>
+        <v>0.09804306191244715</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,28 +9828,28 @@
         <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.09956014923254693</v>
+        <v>-0.1141972469056811</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.04597308735476804</v>
+        <v>0.1306198501928401</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.01566903710505066</v>
+        <v>0.01034902382478908</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,19 +9861,19 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.06962633541946221</v>
+        <v>-0.1115652521310111</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.02670049064692812</v>
+        <v>0.02049838303075886</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02020252685265402</v>
+        <v>-0.06534760628593012</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -9888,19 +9888,19 @@
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.05654829371152682</v>
+        <v>-0.06445346783019872</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.03260239039583396</v>
+        <v>0.07744422216155608</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.07948413711343835</v>
+        <v>-0.01089552303548035</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
@@ -9912,25 +9912,25 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.04279766985326542</v>
+        <v>0.04102649269669122</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.03405907110714274</v>
+        <v>-0.05625292850908149</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.01785420364338167</v>
+        <v>0.03697498704670408</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,52 +9939,52 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.06481206191853912</v>
+        <v>-0.09017157276112256</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.04857398069934623</v>
+        <v>0.06792165384518431</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.06141271074858666</v>
+        <v>0.04712976416515854</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.09676678768679854</v>
+        <v>-0.04600162490206035</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.02189400075855302</v>
+        <v>0.06463538350070283</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0385021574411706</v>
+        <v>-0.03290921650161128</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,49 +9993,49 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.1073685306185436</v>
+        <v>-0.1387932793126001</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.05535807615636663</v>
+        <v>0.1355348356088666</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.01602210275851912</v>
+        <v>0.0004353556405965672</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01570819638133009</v>
+        <v>-0.1002483270032024</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.08091680409129405</v>
+        <v>0.09151761182701044</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.05368721218102562</v>
+        <v>0.02770494746959622</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10044,22 +10044,22 @@
         <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004605390004266514</v>
+        <v>0.003323729721730207</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.04340389757561664</v>
+        <v>0.05540991035798049</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.01261893865371061</v>
+        <v>-0.01798797150187113</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
@@ -10068,37 +10068,37 @@
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.01908413477880015</v>
+        <v>-0.1301038882471704</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.06077536205092272</v>
+        <v>0.04421928079362451</v>
       </c>
       <c r="GC17" t="n">
         <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1524331165467947</v>
+        <v>0.2766652365959882</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01732386259276928</v>
+        <v>0.01461730692873143</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09628076010199617</v>
+        <v>-0.09944705129274582</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -10133,76 +10133,76 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1181909210224796</v>
+        <v>0.4051631676172264</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02376875767081438</v>
+        <v>-0.03679136101584936</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1104188379405928</v>
+        <v>-0.09981354491542808</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02097475041406945</v>
+        <v>0.07972991759126453</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.004632625469266452</v>
+        <v>-0.05032616753238319</v>
       </c>
       <c r="X18" t="n">
-        <v>0.008175468572130948</v>
+        <v>0.0004129723363557178</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01582053480093209</v>
+        <v>-0.007077976741868872</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01361899011361925</v>
+        <v>-0.1280923392875534</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.002321032671899416</v>
+        <v>-0.04470492819868387</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.008957753851892425</v>
+        <v>0.02910190723272345</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.01568782263889794</v>
+        <v>-0.01775591168004802</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01959873269441719</v>
+        <v>-0.02262675618932503</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1104861007327542</v>
+        <v>0.2858731239894747</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,16 +10250,16 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.01562535082644676</v>
+        <v>-0.1308502559963823</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.04126303322049901</v>
+        <v>-0.04418566850487775</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
@@ -10268,52 +10268,52 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04545154283522024</v>
+        <v>0.03889108597492481</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.03461821522687651</v>
+        <v>-0.04568065182595732</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.04822585103563863</v>
+        <v>-0.06609059754520116</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.04729066500336707</v>
+        <v>0.0376723499114313</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02443842613377836</v>
+        <v>0.04983892457368928</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.008719571269782891</v>
+        <v>-0.009049713635857192</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
         <v>0</v>
@@ -10322,7 +10322,7 @@
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.05186019977749944</v>
+        <v>0.2187135292254934</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.002084628209721988</v>
+        <v>-0.02530748308728833</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.01841265568583186</v>
+        <v>-0.03004404518185327</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10349,19 +10349,19 @@
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.02871887375822995</v>
+        <v>-0.083071934494247</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.003397009142683659</v>
+        <v>0.01459921187208159</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.02659828319553253</v>
+        <v>0.04457633071013095</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
@@ -10370,40 +10370,40 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01714864873457655</v>
+        <v>-0.1701967880996918</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.01078841727087699</v>
+        <v>0.1137842710482103</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01081096241194123</v>
+        <v>0.04446423333687541</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01983786734295008</v>
+        <v>-0.08743090653111493</v>
       </c>
       <c r="CX18" t="n">
         <v>-0</v>
@@ -10412,13 +10412,13 @@
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.002509108222904273</v>
+        <v>-0.005383267347404652</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02620735319339526</v>
+        <v>0.05050433495440565</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
@@ -10427,22 +10427,22 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.02880380457741337</v>
+        <v>-0.05152734012074204</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.01342003007236048</v>
+        <v>-0.1229724809928559</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0001638632167931798</v>
+        <v>-0.001017976268622095</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10454,49 +10454,49 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01990140842740624</v>
+        <v>-0.08652114596088839</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.006894525294751759</v>
+        <v>0.06110914255418778</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.007174770226943719</v>
+        <v>-0.03059594775219226</v>
       </c>
       <c r="DT18" t="n">
         <v>0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.01460591712045438</v>
+        <v>-0.01076054709688754</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.004956583732357894</v>
+        <v>0.1080133732037185</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.01482853241879798</v>
+        <v>-0.05609400044993199</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10511,7 +10511,7 @@
         <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01298339931201821</v>
+        <v>-0.00621584312693959</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
@@ -10520,37 +10520,37 @@
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.000389744477588285</v>
+        <v>-0.02624383545209672</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.01610239377842925</v>
+        <v>0.02248262039285562</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.006274830746184726</v>
+        <v>0.008985563710553809</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.005393424981902175</v>
+        <v>-0.0852887596476635</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.01399395413146378</v>
+        <v>0.06916470722539245</v>
       </c>
       <c r="EU18" t="n">
         <v>-0</v>
@@ -10565,34 +10565,34 @@
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.02065905201687365</v>
+        <v>-0.09827151677538741</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.0007738138880825678</v>
+        <v>-0.0103124887323753</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.02934942958671252</v>
+        <v>0.04385872231423196</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.003877500525064404</v>
+        <v>-0.1431317770600221</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
@@ -10601,25 +10601,25 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.01889907154221452</v>
+        <v>0.107106509898079</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.02312923113270612</v>
+        <v>0.04147212498946839</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>9.00413023802102e-05</v>
+        <v>0.0008042966551225516</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,10 +10628,10 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.001554256612973878</v>
+        <v>-0.006725216168250298</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.01634388451809678</v>
+        <v>-0.06139301039860492</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
@@ -10640,25 +10640,25 @@
         <v>-0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.01529102594445008</v>
+        <v>-0.005310766045629676</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.01994598042521753</v>
+        <v>-0.005014955790628036</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.814558856498351</v>
+        <v>0.7743721568326468</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3694424449895685</v>
+        <v>-0.4028256590219762</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2610710617728629</v>
+        <v>-0.1608247373151219</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10702,16 +10702,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5887008607101424</v>
+        <v>0.8575322033385265</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3320050662244325</v>
+        <v>-0.5489314331759432</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2739176542090175</v>
+        <v>-0.2960096047166896</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10729,70 +10729,70 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1811668986350252</v>
+        <v>0.1151392374698686</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.06586459973603702</v>
+        <v>-0.1422891243571437</v>
       </c>
       <c r="W19" t="n">
-        <v>0.05672053356250729</v>
+        <v>-0.1932395343379771</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1186413351537076</v>
+        <v>-0.001433879704009877</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.01665218105499969</v>
+        <v>-0.1701805124449749</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.01104404196727625</v>
+        <v>-0.1542205423333786</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.05174401319384529</v>
+        <v>0.224853368053527</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.05119281766279716</v>
+        <v>-0.1480541219379576</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.08091053624712985</v>
+        <v>0.04766897025584807</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -10807,28 +10807,28 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.6437610154405697</v>
+        <v>0.7755925233473966</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.02707394275491741</v>
+        <v>-0.2115516881355901</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.02564678249502942</v>
+        <v>-0.3985159429767505</v>
       </c>
       <c r="AY19" t="n">
         <v>-0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>-0</v>
@@ -10837,16 +10837,16 @@
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.09184051633371165</v>
+        <v>-0.03085498876302534</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.1852382970902935</v>
+        <v>-0.09218744727994389</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.3218143580505773</v>
+        <v>-0.009724279409832745</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -10855,7 +10855,7 @@
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,22 +10864,22 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1909884077743872</v>
+        <v>0.03409828223226927</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.03444627620540652</v>
+        <v>0.03896355167109838</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.158000149113966</v>
+        <v>0.1582249750564755</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
@@ -10888,28 +10888,28 @@
         <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.3214936969610648</v>
+        <v>0.5004405534800745</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.01825217472718666</v>
+        <v>-0.2696306433587686</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.04675349021872927</v>
+        <v>-0.1777137866623144</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -10918,46 +10918,46 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.1544639896473873</v>
+        <v>-0.2577029649524061</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.04397308306940965</v>
+        <v>0.18898724796374</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.01159078278402481</v>
+        <v>0.07048025864490175</v>
       </c>
       <c r="CI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.04050905614833922</v>
+        <v>-0.3375060575163228</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.1487783606844622</v>
+        <v>0.3872941853124368</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.1044021923796269</v>
+        <v>0.1387519275480056</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
@@ -10966,55 +10966,55 @@
         <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.1177715420343642</v>
+        <v>-0.2358928839361326</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.07426365826360944</v>
+        <v>0.2248011678776271</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.01897265630634832</v>
+        <v>0.05998651769449578</v>
       </c>
       <c r="DA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.1065106209254141</v>
+        <v>-0.1164325864383836</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.07387292541359017</v>
+        <v>0.04382205345287651</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.009802358999850458</v>
+        <v>-0.1347788267733892</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
       </c>
       <c r="DK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
@@ -11026,19 +11026,19 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.09299366873609238</v>
+        <v>-0.1554033437813955</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.006677230821150092</v>
+        <v>-0.07232490044120418</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.07082852009728233</v>
+        <v>-0.01866175988771286</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11053,76 +11053,76 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.02578485900975972</v>
+        <v>0.1299303364810217</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0.003625385206844097</v>
+        <v>0.08052104509266882</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.0827015170705887</v>
+        <v>-0.06753491411883142</v>
       </c>
       <c r="EB19" t="n">
         <v>0</v>
       </c>
       <c r="EC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED19" t="n">
         <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.1217148965312338</v>
+        <v>-0.1163260313218416</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.04118803072275574</v>
+        <v>0.1294549965929273</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.111747420195173</v>
+        <v>0.07994167843643647</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
         <v>-0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.06585369386223421</v>
+        <v>-0.08591719315150941</v>
       </c>
       <c r="EQ19" t="n">
         <v>0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.05018055111216516</v>
+        <v>0.1204095047558454</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.01679097566624372</v>
+        <v>-0.0959981351443006</v>
       </c>
       <c r="ET19" t="n">
         <v>-0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
@@ -11131,46 +11131,46 @@
         <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.1179104460464998</v>
+        <v>-0.2748441919827036</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.06117089714987566</v>
+        <v>0.2282687890757414</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.01242491940181837</v>
+        <v>0.03689716696193516</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.018830928417315</v>
+        <v>-0.1466007055433659</v>
       </c>
       <c r="FI19" t="n">
         <v>-0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.08341860134877638</v>
+        <v>0.1847917533473073</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.08571090074687431</v>
+        <v>0.07330100900129977</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11179,31 +11179,31 @@
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.0003846157789091716</v>
+        <v>0.0009220079607317294</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.009089104049799667</v>
+        <v>0.1896434583623305</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.001951714586045707</v>
+        <v>-0.007513472709273896</v>
       </c>
       <c r="FU19" t="n">
         <v>-0</v>
       </c>
       <c r="FV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW19" t="n">
         <v>0</v>
@@ -11212,31 +11212,31 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.02366946561614677</v>
+        <v>-0.1906811314074078</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.04875960548677771</v>
+        <v>0.1157180957983966</v>
       </c>
       <c r="GC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -11244,19 +11244,19 @@
         <v>-0</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.3726967537253744</v>
+        <v>-0.2410372191725468</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05896042705029474</v>
+        <v>0.03647386376605715</v>
       </c>
       <c r="F20" t="n">
-        <v>0.697909250809601</v>
+        <v>0.5678582384255766</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
@@ -11271,7 +11271,7 @@
         <v>-0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2824943487624091</v>
+        <v>-0.3058212769646039</v>
       </c>
       <c r="L20" t="n">
         <v>-0</v>
@@ -11280,10 +11280,10 @@
         <v>-0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.006293761306071419</v>
+        <v>0.1834917991267716</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6554149451590646</v>
+        <v>0.5716230114982045</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
@@ -11298,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.02194191516164547</v>
+        <v>-0.1050094809213988</v>
       </c>
       <c r="U20" t="n">
         <v>-0</v>
@@ -11307,10 +11307,10 @@
         <v>-0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.04029802914639491</v>
+        <v>0.1429191235025286</v>
       </c>
       <c r="X20" t="n">
-        <v>0.05152677559610106</v>
+        <v>0.06396310651479091</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -11319,25 +11319,25 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.09077095951516692</v>
+        <v>-0.02026510485107434</v>
       </c>
       <c r="AD20" t="n">
         <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.0271221839447736</v>
+        <v>0.2264768815590124</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.04870246300232575</v>
+        <v>0.1779966642371245</v>
       </c>
       <c r="AH20" t="n">
         <v>-0</v>
@@ -11352,22 +11352,22 @@
         <v>-0</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.04571992205040996</v>
+        <v>-0.1013153772834871</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN20" t="n">
         <v>-0</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.03170262886093994</v>
+        <v>-0.07799612330200471</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.10954695319397</v>
+        <v>0.165848277234564</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -11379,46 +11379,46 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.3348555323807492</v>
+        <v>-0.6290004905090876</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.1063100205498047</v>
+        <v>0.05658925997539568</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.3922157336600098</v>
+        <v>0.3104315717842409</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
         <v>-0</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
         <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.1360153566571911</v>
+        <v>0.08092143141975805</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
         <v>-0</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.06751261099052014</v>
+        <v>0.2122692419420564</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.1241688048139935</v>
+        <v>0.1397791463522589</v>
       </c>
       <c r="BI20" t="n">
         <v>-0</v>
@@ -11427,13 +11427,13 @@
         <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>-0.06126948265311733</v>
+        <v>-0.03741025307506841</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -11442,10 +11442,10 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>-0.0580188123572314</v>
+        <v>-0.1576689253461701</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.01263603506089547</v>
+        <v>-0.03265986833618697</v>
       </c>
       <c r="BR20" t="n">
         <v>-0</v>
@@ -11460,22 +11460,22 @@
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>-0.1753915680598506</v>
+        <v>-0.3413545710932075</v>
       </c>
       <c r="BW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX20" t="n">
         <v>-0</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.04432026942734722</v>
+        <v>0.08944589897227022</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.2278350599246159</v>
+        <v>0.2561327509894501</v>
       </c>
       <c r="CA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="n">
         <v>0</v>
@@ -11487,49 +11487,49 @@
         <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.09341955221617383</v>
+        <v>0.123636531526126</v>
       </c>
       <c r="CF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.00373301224122988</v>
+        <v>-0.04292180722330543</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0.1231919952967107</v>
+        <v>-0.159079071029775</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK20" t="n">
         <v>-0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
         <v>-0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.04248884987256591</v>
+        <v>0.2535197015210727</v>
       </c>
       <c r="CO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP20" t="n">
         <v>0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.09683882683589859</v>
+        <v>-0.2315433448111837</v>
       </c>
       <c r="CR20" t="n">
-        <v>0.03859126005959822</v>
+        <v>-0.2047187216238544</v>
       </c>
       <c r="CS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT20" t="n">
         <v>0</v>
@@ -11538,82 +11538,82 @@
         <v>0</v>
       </c>
       <c r="CV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.06545875321159786</v>
+        <v>0.1036041124751988</v>
       </c>
       <c r="CX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY20" t="n">
         <v>-0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.00528268118003386</v>
+        <v>-0.037428829409687</v>
       </c>
       <c r="DA20" t="n">
-        <v>-0.1217308743917705</v>
+        <v>-0.1616516553978138</v>
       </c>
       <c r="DB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC20" t="n">
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE20" t="n">
         <v>-0</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.03691589337331382</v>
+        <v>0.02923727001591898</v>
       </c>
       <c r="DG20" t="n">
         <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.04650935147732239</v>
+        <v>0.1180232833460586</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0.01208258348571886</v>
+        <v>0.007718210305239765</v>
       </c>
       <c r="DK20" t="n">
         <v>-0</v>
       </c>
       <c r="DL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.01995308325425786</v>
+        <v>0.02197591557177669</v>
       </c>
       <c r="DP20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ20" t="n">
         <v>-0</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.01505598459651249</v>
+        <v>-0.04308022322231799</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.04404014803248608</v>
+        <v>-0.03180045893446423</v>
       </c>
       <c r="DT20" t="n">
         <v>0</v>
       </c>
       <c r="DU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV20" t="n">
         <v>0</v>
@@ -11622,22 +11622,22 @@
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.01552497769142185</v>
+        <v>-0.1040453533872096</v>
       </c>
       <c r="DY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ20" t="n">
         <v>-0</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.04473143762093199</v>
+        <v>-0.01708804962866457</v>
       </c>
       <c r="EB20" t="n">
-        <v>-0.03839388202256241</v>
+        <v>-0.1105894421440654</v>
       </c>
       <c r="EC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED20" t="n">
         <v>-0</v>
@@ -11646,79 +11646,79 @@
         <v>0</v>
       </c>
       <c r="EF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG20" t="n">
-        <v>0.05892154376909624</v>
+        <v>0.01189898797432087</v>
       </c>
       <c r="EH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>-0.06313518964395591</v>
+        <v>0.03627433491472688</v>
       </c>
       <c r="EK20" t="n">
-        <v>-0.1125955782362459</v>
+        <v>-0.04525752658833805</v>
       </c>
       <c r="EL20" t="n">
         <v>0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.05289811842872196</v>
+        <v>0.036161373654626</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER20" t="n">
         <v>0</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.03921479603405107</v>
+        <v>0.01756874465383368</v>
       </c>
       <c r="ET20" t="n">
-        <v>-0.01311422225368966</v>
+        <v>-0.1026331101599939</v>
       </c>
       <c r="EU20" t="n">
         <v>-0</v>
       </c>
       <c r="EV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.0646123070524824</v>
+        <v>0.1313423484894939</v>
       </c>
       <c r="EZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.01883222104779485</v>
+        <v>-0.0118590539399404</v>
       </c>
       <c r="FC20" t="n">
-        <v>-0.1176979720236587</v>
+        <v>-0.1514170137185792</v>
       </c>
       <c r="FD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE20" t="n">
         <v>-0</v>
@@ -11730,34 +11730,34 @@
         <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.04843789615613429</v>
+        <v>0.1417007925876318</v>
       </c>
       <c r="FI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ20" t="n">
         <v>0</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.02456586071478184</v>
+        <v>-0.04501558699187719</v>
       </c>
       <c r="FL20" t="n">
-        <v>0.08583968019243599</v>
+        <v>0.1604631164863995</v>
       </c>
       <c r="FM20" t="n">
         <v>-0</v>
       </c>
       <c r="FN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO20" t="n">
         <v>-0</v>
       </c>
       <c r="FP20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.003689742480137886</v>
+        <v>0.02825544787038251</v>
       </c>
       <c r="FR20" t="n">
         <v>0</v>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.001314661361926086</v>
+        <v>-2.207100702877134e-05</v>
       </c>
       <c r="FU20" t="n">
-        <v>-0.04407162145571278</v>
+        <v>-0.1359465910441016</v>
       </c>
       <c r="FV20" t="n">
         <v>0</v>
@@ -11778,31 +11778,31 @@
         <v>-0</v>
       </c>
       <c r="FX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.02374566029004647</v>
+        <v>0.03311670233029738</v>
       </c>
       <c r="GA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB20" t="n">
         <v>0</v>
       </c>
       <c r="GC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.03382171836858636</v>
+        <v>-0.02016906272968417</v>
       </c>
       <c r="GE20" t="n">
         <v>0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
         <v>-0</v>
